--- a/범운해운항공_전체데이터_통합백업_2026-10-18.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-18.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": "경기도 김포시 풍무동 326-5번지 2층"}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "ESI"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}, "ESI": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 22000, "1CBM당단가": 3500000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "ESI": {"사업자등록번호": "", "이메일": "", "담당자": "정재국대표님", "전화번호": "", "주소": ""}}, "ledger_data": [{"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)5710", "금액(원)": 70000, "적요": "장부 메모", "작성자": "이상복"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양 김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-15", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 익스프레스저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-17", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-18.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-18.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z49"/>
+  <dimension ref="A1:Z50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6215,6 +6215,124 @@
         </is>
       </c>
       <c r="Z49" t="inlineStr">
+        <is>
+          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BW-2026-053</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1ZRR43520333795803</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>아코글로벌</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Olga Voloshina</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>37×37×25cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.035 CBM</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>9</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>✈ 항공/해상 선적 완료 (운송 중)</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T50" t="n">
+        <v>351000</v>
+      </c>
+      <c r="U50" t="n">
+        <v>235000</v>
+      </c>
+      <c r="V50" t="n">
+        <v>116000</v>
+      </c>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
         <is>
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
